--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.85353</v>
+        <v>18.09638</v>
       </c>
       <c r="D2" t="n">
-        <v>18.04606</v>
+        <v>17.5221</v>
       </c>
       <c r="E2" t="n">
-        <v>17.63269</v>
+        <v>17.68204</v>
       </c>
       <c r="F2" t="n">
-        <v>46.5457</v>
+        <v>44.51532</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05381</v>
+        <v>0.05265</v>
       </c>
       <c r="H2" t="n">
-        <v>1.96046</v>
+        <v>1.94531</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.49259</v>
+        <v>17.75006</v>
       </c>
       <c r="D3" t="n">
-        <v>17.80626</v>
+        <v>17.35019</v>
       </c>
       <c r="E3" t="n">
-        <v>17.65083</v>
+        <v>17.72346</v>
       </c>
       <c r="F3" t="n">
-        <v>45.5136</v>
+        <v>44.97235</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05336</v>
+        <v>0.05338</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93927</v>
+        <v>1.90369</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.5259</v>
+        <v>17.98495</v>
       </c>
       <c r="D4" t="n">
-        <v>17.08503</v>
+        <v>17.64893</v>
       </c>
       <c r="E4" t="n">
-        <v>17.46419</v>
+        <v>17.65577</v>
       </c>
       <c r="F4" t="n">
-        <v>44.99269</v>
+        <v>45.08903</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05339</v>
+        <v>0.05393</v>
       </c>
       <c r="H4" t="n">
-        <v>1.92143</v>
+        <v>1.94347</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.73037</v>
+        <v>17.55739</v>
       </c>
       <c r="D6" t="n">
-        <v>16.98003</v>
+        <v>17.15714</v>
       </c>
       <c r="E6" t="n">
-        <v>17.19298</v>
+        <v>17.3388</v>
       </c>
       <c r="F6" t="n">
-        <v>23.698</v>
+        <v>22.56638</v>
       </c>
       <c r="G6" t="n">
-        <v>35.59716</v>
+        <v>35.97138</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.97109</v>
+        <v>17.76765</v>
       </c>
       <c r="D7" t="n">
-        <v>17.37449</v>
+        <v>17.16538</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2827</v>
+        <v>17.60495</v>
       </c>
       <c r="F7" t="n">
-        <v>23.10548</v>
+        <v>22.94252</v>
       </c>
       <c r="G7" t="n">
-        <v>36.272</v>
+        <v>36.88948</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.57646</v>
+        <v>17.51959</v>
       </c>
       <c r="D8" t="n">
-        <v>16.90163</v>
+        <v>16.57525</v>
       </c>
       <c r="E8" t="n">
-        <v>17.44597</v>
+        <v>17.15801</v>
       </c>
       <c r="F8" t="n">
-        <v>23.31788</v>
+        <v>23.15233</v>
       </c>
       <c r="G8" t="n">
-        <v>36.0519</v>
+        <v>36.15328</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.64035</v>
+        <v>0.64131</v>
       </c>
       <c r="D10" t="n">
-        <v>1.15328</v>
+        <v>1.16168</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6460399999999999</v>
+        <v>0.64967</v>
       </c>
       <c r="D11" t="n">
-        <v>1.16139</v>
+        <v>1.17262</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.65176</v>
+        <v>0.65185</v>
       </c>
       <c r="D12" t="n">
-        <v>1.17859</v>
+        <v>1.17432</v>
       </c>
     </row>
   </sheetData>
